--- a/public/plantillas/Plantilla Cursos de Ley.xlsx
+++ b/public/plantillas/Plantilla Cursos de Ley.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_4362BABD075A0368CE4379D9EF41B928EDDFA32F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD37C07-C895-4E0A-AA53-FA87BA865EE6}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_4362BABD075A0368CE4379D9EF41B928EDDFA32F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA32B25-8F1A-4C8C-90D8-98FD0FE13915}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1202,9 +1202,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1225,6 +1222,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3586,9 +3586,9 @@
     <col min="22" max="22" width="31.3984375" style="17" customWidth="1"/>
     <col min="23" max="23" width="34" style="17" customWidth="1"/>
     <col min="24" max="24" width="31.3984375" style="17" customWidth="1"/>
-    <col min="25" max="25" width="10.09765625" style="37" customWidth="1"/>
-    <col min="26" max="26" width="10.09765625" style="42" customWidth="1"/>
-    <col min="27" max="27" width="10.09765625" style="36" customWidth="1"/>
+    <col min="25" max="25" width="10.09765625" style="36" customWidth="1"/>
+    <col min="26" max="26" width="10.09765625" style="41" customWidth="1"/>
+    <col min="27" max="27" width="10.09765625" style="35" customWidth="1"/>
     <col min="28" max="16384" width="10.5" style="3"/>
   </cols>
   <sheetData>
@@ -3665,10 +3665,10 @@
       <c r="X1" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="Y1" s="38" t="s">
+      <c r="Y1" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="Z1" s="40" t="s">
+      <c r="Z1" s="39" t="s">
         <v>216</v>
       </c>
       <c r="AA1" s="30" t="s">
@@ -3748,10 +3748,10 @@
       <c r="X2" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="Y2" s="39" t="s">
+      <c r="Y2" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="Z2" s="41" t="s">
+      <c r="Z2" s="40" t="s">
         <v>224</v>
       </c>
       <c r="AA2" s="16" t="s">
@@ -3834,8 +3834,8 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">

--- a/public/plantillas/Plantilla Cursos de Ley.xlsx
+++ b/public/plantillas/Plantilla Cursos de Ley.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_4362BABD075A0368CE4379D9EF41B928EDDFA32F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA32B25-8F1A-4C8C-90D8-98FD0FE13915}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="11_4362BABD075A0368CE4379D9EF41B928EDDFA32F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02AABC3A-FF33-4E36-A688-5B999222C48E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,19 @@
     <sheet name="People" sheetId="1" r:id="rId1"/>
     <sheet name="Parameters" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -26,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="280">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -829,12 +840,71 @@
   </si>
   <si>
     <t>Validación2</t>
+  </si>
+  <si>
+    <t>promedio</t>
+  </si>
+  <si>
+    <t>puesto</t>
+  </si>
+  <si>
+    <t>modalidad</t>
+  </si>
+  <si>
+    <t>tipo</t>
+  </si>
+  <si>
+    <t>Opcional
+Promedio</t>
+  </si>
+  <si>
+    <t>Opcional
+Puesto</t>
+  </si>
+  <si>
+    <t>Opcional
+Numero Curso</t>
+  </si>
+  <si>
+    <t>Opcional
+Modalidad</t>
+  </si>
+  <si>
+    <t>Opcional
+Tipo</t>
+  </si>
+  <si>
+    <t>Modalidad</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>A distancia</t>
+  </si>
+  <si>
+    <t>Presencial</t>
+  </si>
+  <si>
+    <t>Sincrónico</t>
+  </si>
+  <si>
+    <t>Línea</t>
+  </si>
+  <si>
+    <t>Administrativo</t>
+  </si>
+  <si>
+    <t>numerocurso</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1100,7 +1170,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1225,6 +1295,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1978,13 +2066,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2076,13 +2164,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2174,13 +2262,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2272,13 +2360,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2370,13 +2458,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
@@ -2452,13 +2540,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2534,13 +2622,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2616,13 +2704,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>792480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>32</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2888,13 +2976,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3093,13 +3181,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3117,8 +3205,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18700376" y="554467"/>
-          <a:ext cx="1515036" cy="440615"/>
+          <a:off x="28422600" y="7620"/>
+          <a:ext cx="1514475" cy="440055"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3259,6 +3347,476 @@
             </a:rPr>
             <a:t>EMAIL</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="CuadroTexto 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF5341A7-49D8-4020-F378-93A00E87F166}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25126950" y="0"/>
+          <a:ext cx="1647825" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>PROMEDIO BALANCE</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>3 dígitos decimales)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-CO" sz="1100" b="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="CuadroTexto 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA218920-A762-4F25-81D8-B22E874E946A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18849975" y="552450"/>
+          <a:ext cx="1647825" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>PUESTO OCUPADO</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>(Ejemplo: 1/30)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-CO" sz="1100" b="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="CuadroTexto 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49AE3F27-E62F-432C-BAD3-0080B553211C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22736175" y="552450"/>
+          <a:ext cx="1209675" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>NUMERO CURSO</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-CO" sz="1100" b="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="CuadroTexto 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA9690F3-5945-4425-A60F-FA4D3EAB8FE7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23945850" y="552450"/>
+          <a:ext cx="2238375" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>MODALIDAD</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>(Elegir una opción)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-CO" sz="1100" b="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="CuadroTexto 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5074D522-BE41-44AF-BA37-A2EF17EA56EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="26184225" y="552450"/>
+          <a:ext cx="2238375" cy="447675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>TIPO</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>(Elegir una opción)</a:t>
+          </a:r>
+          <a:endParaRPr lang="es-CO" sz="1100" b="0">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3564,7 +4122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="25.296875" style="34" customWidth="1"/>
@@ -3581,18 +4139,22 @@
     <col min="16" max="16" width="25.8984375" style="17" customWidth="1"/>
     <col min="17" max="17" width="21.59765625" style="17" customWidth="1"/>
     <col min="18" max="18" width="29.3984375" style="17" customWidth="1"/>
-    <col min="19" max="19" width="19.8984375" style="25" customWidth="1"/>
-    <col min="20" max="21" width="27.69921875" style="17" customWidth="1"/>
-    <col min="22" max="22" width="31.3984375" style="17" customWidth="1"/>
-    <col min="23" max="23" width="34" style="17" customWidth="1"/>
-    <col min="24" max="24" width="31.3984375" style="17" customWidth="1"/>
-    <col min="25" max="25" width="10.09765625" style="36" customWidth="1"/>
-    <col min="26" max="26" width="10.09765625" style="41" customWidth="1"/>
-    <col min="27" max="27" width="10.09765625" style="35" customWidth="1"/>
-    <col min="28" max="16384" width="10.5" style="3"/>
+    <col min="19" max="19" width="15.8984375" style="48" customWidth="1"/>
+    <col min="20" max="21" width="29.3984375" style="17" customWidth="1"/>
+    <col min="22" max="22" width="21.59765625" style="45" customWidth="1"/>
+    <col min="23" max="23" width="21.59765625" style="48" customWidth="1"/>
+    <col min="24" max="24" width="19.8984375" style="25" customWidth="1"/>
+    <col min="25" max="26" width="27.69921875" style="17" customWidth="1"/>
+    <col min="27" max="27" width="31.3984375" style="17" customWidth="1"/>
+    <col min="28" max="28" width="34" style="17" customWidth="1"/>
+    <col min="29" max="29" width="31.3984375" style="17" customWidth="1"/>
+    <col min="30" max="30" width="10.09765625" style="36" customWidth="1"/>
+    <col min="31" max="31" width="10.09765625" style="41" customWidth="1"/>
+    <col min="32" max="32" width="10.09765625" style="35" customWidth="1"/>
+    <col min="33" max="16384" width="10.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -3647,35 +4209,50 @@
       <c r="R1" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="S1" s="23" t="s">
+      <c r="S1" s="46" t="s">
+        <v>269</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="V1" s="43" t="s">
+        <v>267</v>
+      </c>
+      <c r="W1" s="46" t="s">
+        <v>268</v>
+      </c>
+      <c r="X1" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="Y1" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="Z1" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="AA1" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="W1" s="12" t="s">
+      <c r="AB1" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="X1" s="12" t="s">
+      <c r="AC1" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="AD1" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="Z1" s="39" t="s">
+      <c r="AE1" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="AA1" s="30" t="s">
+      <c r="AF1" s="30" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
         <v>3</v>
       </c>
@@ -3730,35 +4307,50 @@
       <c r="R2" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="S2" s="47" t="s">
+        <v>279</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="V2" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="W2" s="47" t="s">
+        <v>264</v>
+      </c>
+      <c r="X2" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="Y2" s="13" t="s">
         <v>221</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="Z2" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="AA2" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="AB2" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="AC2" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="Y2" s="38" t="s">
+      <c r="AD2" s="38" t="s">
         <v>225</v>
       </c>
-      <c r="Z2" s="40" t="s">
+      <c r="AE2" s="40" t="s">
         <v>224</v>
       </c>
-      <c r="AA2" s="16" t="s">
+      <c r="AF2" s="16" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G3" s="17"/>
       <c r="H3" s="18"/>
       <c r="I3" s="18"/>
@@ -3769,17 +4361,23 @@
       <c r="N3" s="18"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="lysacY5PmYeqe/3EOsM+2h6wdqucrcRs0sub4Q2GoD6cY4BNWlhH1mr9iuLXxiWDGG57L6rPo9JMINma6QIL+A==" saltValue="cLbBeXtUR3ubwoSk6y5J1Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SYqJKuHN2lC31BjnWf9oDfIaivfMhe0xjhBedIy75JrYaHG+XLTBhqL6/fGPwBWGesYbdOoVF+vE8W6/Epb6Ow==" saltValue="oe0DIOzUw4UEz2bePJmo7w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="A3:R354 T3:AA354" name="Rango1"/>
-    <protectedRange sqref="S3:S354" name="Rango1_1"/>
+    <protectedRange sqref="Y3:AF354 A3:Q354 R3:W354" name="Rango1"/>
+    <protectedRange sqref="X3:X354" name="Rango1_1"/>
   </protectedRanges>
+  <dataValidations count="1">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1:V1048576" xr:uid="{D3C363B7-4E9A-4864-9853-5AD64DEDBB6C}">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Parameters!$F$4:$F$5</xm:f>
@@ -3810,6 +4408,18 @@
           </x14:formula1>
           <xm:sqref>Q3:Q1048576</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{30C46DE4-B56E-4541-9217-CE68A5089EAD}">
+          <x14:formula1>
+            <xm:f>Parameters!$M$4:$M$6</xm:f>
+          </x14:formula1>
+          <xm:sqref>T1:T1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{960D1AA9-76CF-4FDA-B177-0DB0CD677065}">
+          <x14:formula1>
+            <xm:f>Parameters!$N$4:$N$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>U1:W1048576</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -3818,7 +4428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J196"/>
+  <dimension ref="A1:N196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" hidden="1" customWidth="1"/>
@@ -3828,16 +4438,16 @@
     <col min="10" max="10" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H2" s="42"/>
       <c r="I2" s="42"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
@@ -3850,8 +4460,14 @@
       <c r="J3" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>272</v>
+      </c>
+      <c r="N3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
         <v>20</v>
       </c>
@@ -3864,8 +4480,14 @@
       <c r="J4" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M4" t="s">
+        <v>275</v>
+      </c>
+      <c r="N4" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
         <v>22</v>
       </c>
@@ -3878,8 +4500,14 @@
       <c r="J5" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M5" t="s">
+        <v>274</v>
+      </c>
+      <c r="N5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
         <v>23</v>
       </c>
@@ -3889,8 +4517,11 @@
       <c r="J6" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>24</v>
       </c>
@@ -3901,7 +4532,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>25</v>
       </c>
@@ -3909,7 +4540,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>26</v>
       </c>
@@ -3917,7 +4548,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>27</v>
       </c>
@@ -3925,7 +4556,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>28</v>
       </c>
@@ -3933,7 +4564,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>29</v>
       </c>
@@ -3941,7 +4572,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
         <v>30</v>
       </c>
@@ -3949,7 +4580,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
         <v>31</v>
       </c>
@@ -3957,7 +4588,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
         <v>32</v>
       </c>
@@ -3965,7 +4596,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
         <v>33</v>
       </c>
